--- a/meta/16-6-1.xlsx
+++ b/meta/16-6-1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
@@ -94,19 +94,10 @@
     <t>8. Ссылки и документация</t>
   </si>
   <si>
-    <t>Цель 16. Содействие построению миролюбивого и открытого общества в интересах устойчивого развития, обеспечение доступа к правосудию для всех и создание эффективных, подотчетных и основанных на широком участии учреждений на всех уровнях</t>
-  </si>
-  <si>
     <t>16.6.  Создать эффективные, подотчетные и прозрачные учреждения на всех уровнях</t>
   </si>
   <si>
     <t>Министерство финансов Кыргызской Ремпублики (Управление бюджетной политики)</t>
-  </si>
-  <si>
-    <t>Омурова Т.А.</t>
-  </si>
-  <si>
-    <t>МФ КР: +996-0312-62-53-13 (доб 1110, 1112)</t>
   </si>
   <si>
     <t>www.minfin.kg</t>
@@ -123,9 +114,6 @@
   <si>
     <t>Данные о государственных расходах - данные Центрального казначейства Министерства финансов КР из отчетов по исполнению государственного, республиканского и местных бюджетов. 
 Закон о республиканском бюджете на соответствующие годы.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> t.omurova@minfin.kg</t>
   </si>
   <si>
     <t>Отчеты ЦК МФ КР об исполнении государственного, республиканского и местных бюджетов на годовой основе. Закон о республиканском бюджете на соответствующие годы.</t>
@@ -153,13 +141,25 @@
   </si>
   <si>
     <t xml:space="preserve">16.6.1 Первичные расходы правительства в процентном отношении к первоначальному утвержденному бюджету в разбивке по секторам (по кодам бюджетной классификации или аналогичным категориям) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 16. Содействие построению миролюбивого и открытого общества в интересах устойчивого развития, обеспечение доступа к правосудию для всех и создание эффективных, подотчетных и основанных на широком участии учреждений на всех уровнях</t>
+  </si>
+  <si>
+    <t>Айдарбек у Т.</t>
+  </si>
+  <si>
+    <t>t.aidarbekov@minfin.kg</t>
+  </si>
+  <si>
+    <t>МФ КР: +996-0312-62-53-13 (+ 1110)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +189,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -233,7 +240,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -245,12 +252,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -314,7 +324,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -349,7 +359,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -577,188 +587,188 @@
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>26</v>
+      <c r="B2" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>27</v>
+      <c r="B3" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>44</v>
+      <c r="B4" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="6"/>
     </row>
     <row r="6" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>28</v>
+      <c r="B6" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>29</v>
+      <c r="B7" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>36</v>
+      <c r="B8" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>30</v>
+      <c r="B9" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>31</v>
+      <c r="B10" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="6"/>
     </row>
     <row r="12" spans="1:2" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>32</v>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>33</v>
+      <c r="B13" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>34</v>
+      <c r="B14" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:2" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>35</v>
+      <c r="B16" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>37</v>
+      <c r="B17" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="6"/>
     </row>
     <row r="19" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>38</v>
+      <c r="B19" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>39</v>
+      <c r="B20" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5"/>
+      <c r="B21" s="7"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" s="6"/>
     </row>
     <row r="23" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>40</v>
+      <c r="B23" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>41</v>
+      <c r="B24" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>42</v>
+      <c r="B25" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>43</v>
+      <c r="B26" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
